--- a/02_加值成品/八下/八下5-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下5-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下5-2 常見有機化合物　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下5-2 常見有機化合物　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>提供人體主要能量的有機物？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>蛋白質</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>算</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>有機聚合物</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>醣類</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>供能</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>建構身體、組成酵素的是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>蛋白質</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>葡萄糖</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>胺基酸</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>脂質</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>建構</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>儲存能量、保溫的有機物？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>單體</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>脂質</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>醣類</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>算</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>儲能</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>由小分子重複連接的大分子？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>醣類</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>胺基酸</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>有機聚合物</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>蛋白質</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>高分子</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>澱粉屬於哪類？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>人造</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>算</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>脂質</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>醣類</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>多醣</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>塑膠屬於哪類有機物？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>單體</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>醣類</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>脂質</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>有機聚合物</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>人造</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>蛋白質由什麼組成？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>醣類</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>胺基酸</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>脂質</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>有機聚合物</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>單元</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>葡萄糖屬於哪類？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>醣類</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>算</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>脂質</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>蛋白質</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>單醣</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>人體主要能量來源的養分是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>單體</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>有機聚合物</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>醣類</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>算</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>供能</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>酵素本質屬哪類有機物？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>單體</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>胺基酸</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>蛋白質</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>脂質</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>蛋白</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下5-2 常見有機化合物　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下5-2 常見有機化合物　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>米飯麵包主要提供？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>醣類</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>胺基酸</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>脂質</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>人造</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>能量</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>肉蛋豆主要提供？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>蛋白質</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>算</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>人造</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>脂質</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>建構</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>橡膠與纖維屬於？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>醣類</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>脂質</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>有機聚合物</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>單體</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>高分子</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>聚合物的小分子單元稱？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>不易(疏水)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>胺基酸</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>脂質</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>單體</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>monomer</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>脂質溶於水嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>不易(疏水)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>葡萄糖</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>人造</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>單體</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>油性</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>酵素本質是哪類有機物？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>有機聚合物</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>胺基酸</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>蛋白質</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>葡萄糖</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>生物催化</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>多醣不甜也算醣嗎？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>胺基酸</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>算</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>有機聚合物</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>脂質</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>如澱粉</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>天然聚合物例子？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>單位質量含能量高</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>醣類快速供能脂質儲存能量</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>聚合物穩定造成污染</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>澱粉/纖維素/蛋白質</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>天然</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>澱粉是由許多什麼連接的多醣？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>葡萄糖</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>蛋白質</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>有機聚合物</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>脂質</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>聚合</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>塑膠是天然還人造聚合物？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>蛋白質</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>醣類</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>脂質</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>人造</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>人造</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下5-2 常見有機化合物　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下5-2 常見有機化合物　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>聚合物如何由單體形成？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>生長修復與酵素功能</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>許多小分子單體重複連接</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>單位質量含能量高</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>醣類快速供能脂質儲存能量</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>聚合</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>比較天然與人造聚合物各一例？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>許多小分子單體重複連接</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>生長修復與酵素功能</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>澱粉/纖維素/蛋白質</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>天然:纖維素;人造:塑膠</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>對比</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>為何脂質適合儲能？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>澱粉/纖維素/蛋白質</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>單位質量含能量高</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>天然:纖維素;人造:塑膠</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>由不同胺基酸序列決定</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>儲能</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>蛋白質功能為何多樣？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>澱粉/纖維素/蛋白質</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>由不同胺基酸序列決定</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>單位質量含能量高</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>醣類快速供能脂質儲存能量</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>多樣</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>澱粉與葡萄糖關係？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>澱粉是葡萄糖聚合成的多醣</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>聚合物穩定造成污染</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>天然:纖維素;人造:塑膠</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>許多小分子單體重複連接</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>聚合</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>塑膠難分解對環境的影響？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>醣類快速供能脂質儲存能量</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>聚合物穩定造成污染</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>澱粉/纖維素/蛋白質</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>生長修復與酵素功能</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>環境</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>人體缺乏蛋白質可能影響？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>澱粉/纖維素/蛋白質</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>生長修復與酵素功能</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>天然:纖維素;人造:塑膠</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>由不同胺基酸序列決定</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>健康</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>為何說碳鏈能力造就這些大分子？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>碳可連成長鏈支撐聚合</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>聚合物穩定造成污染</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>由不同胺基酸序列決定</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>許多小分子單體重複連接</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>碳鍵</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何蛋白質能有多種功能？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>澱粉/纖維素/蛋白質</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>許多小分子單體重複連接</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>澱粉是葡萄糖聚合成的多醣</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>由不同胺基酸序列決定</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>多樣</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>比較醣類與脂質作為能量來源？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>聚合物穩定造成污染</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>許多小分子單體重複連接</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>天然:纖維素;人造:塑膠</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>醣類快速供能脂質儲存能量</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>對比</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下5-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下5-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>供能</t>
+          <t>供能：像米飯、麵包這類含醣的食物，是人體最主要、最快速的能量來源</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>建構</t>
+          <t>建構：身體的肌肉、皮膚等組織以及幫助反應的酵素，大多是由蛋白質構成的</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>儲能</t>
+          <t>儲能：脂質可以把多餘的能量儲存起來，還能包覆在身體外層幫助保溫</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>高分子</t>
+          <t>高分子：把很多相同的小分子一個接一個連接起來，就會組成這種巨大的分子</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>多醣</t>
+          <t>多醣：澱粉是由很多個小的醣分子連接組成的，屬於醣類家族中的多醣</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>人造</t>
+          <t>人造：塑膠是人工把小分子單體連接成的巨大分子，屬於人造的有機聚合物</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>單元</t>
+          <t>單元：胺基酸就像一顆顆積木，許多胺基酸串連起來就組成了蛋白質</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>單醣</t>
+          <t>單醣：葡萄糖是結構最簡單、不能再分解的醣分子，屬於單醣</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>供能</t>
+          <t>供能：醣類是人體最主要、最快速的能量來源，日常飲食中的澱粉、糖類都屬於醣類</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>蛋白</t>
+          <t>蛋白：酵素的化學本質是蛋白質，由胺基酸依特定順序連接而成</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>能量</t>
+          <t>能量：米飯和麵包裡含有大量澱粉，屬於醣類，能提供身體活動所需的能量</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>建構</t>
+          <t>建構：肉類、蛋類、豆類這些食物富含蛋白質，能提供身體生長修復所需的原料</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>高分子</t>
+          <t>高分子：橡膠和纖維都是由小分子單體重複連接而成的巨大分子，屬於有機聚合物</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>monomer</t>
+          <t>monomer：組成聚合物的最基本重複單位，就叫做單體</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>油性</t>
+          <t>油性：脂質具有像油一樣的性質，不容易和水互相混合溶解</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>生物催化</t>
+          <t>生物催化：酵素是由蛋白質構成的，它能幫助身體裡的反應加快進行，是一種生物催化劑</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>如澱粉</t>
+          <t>如澱粉：澱粉雖然吃起來不會像糖一樣甜，但化學結構上仍屬於醣類家族，只是分子比較大</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>天然</t>
+          <t>天然：這些聚合物是自然界生物體內原本就存在的大分子，不需要人工合成</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>聚合</t>
+          <t>聚合：澱粉是由大量葡萄糖分子一個接一個連接聚合而成的多醣類</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>人造</t>
+          <t>人造：塑膠是人類利用化學方法合成出來的聚合物，並非自然界天然生成的物質</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>聚合</t>
+          <t>聚合：許多相同或相似的小分子單體，像串珠子一樣一個接一個連接起來，就形成了巨大的聚合物分子</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>對比：纖維素是植物細胞壁裡天然存在的聚合物，塑膠則是人類用化學方法合成出來的聚合物</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>儲能</t>
+          <t>儲能：相同重量的脂質比醣類和蛋白質能儲存更多的能量，所以身體會用脂質長期儲存能量</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>多樣</t>
+          <t>多樣：胺基酸排列的順序和種類組合不同，會讓蛋白質摺疊成不同形狀，因而具有各種不同的功能</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>聚合</t>
+          <t>聚合：澱粉其實是由很多個葡萄糖分子一個接一個連接串起來組成的大分子</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>環境</t>
+          <t>環境：塑膠這種聚合物結構非常穩定，微生物很難把它分解掉，長期累積下來就造成環境污染</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>健康</t>
+          <t>健康：蛋白質不足會讓身體生長和傷口修復變慢，體內幫助反應進行的酵素功能也會受到影響</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>碳鍵</t>
+          <t>碳鍵：碳原子能一個接一個穩固地連接成長長的鏈狀骨架，這種能力正是這些巨大有機分子能夠形成的基礎</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>多樣</t>
+          <t>多樣：蛋白質是由二十幾種胺基酸依不同順序、數量排列組合而成，不同的胺基酸序列會摺疊出不同的立體結構，因此能執行運輸、催化、結構支持等各式各樣的功能</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>對比：醣類容易被分解利用，能快速提供身體所需能量；脂質則能量密度較高，適合以脂肪的形式長期儲存，在醣類不足時再被分解利用</t>
         </is>
       </c>
     </row>
